--- a/sheets/S08A22P153.xlsx
+++ b/sheets/S08A22P153.xlsx
@@ -463,7 +463,7 @@
     <t>Sagar Rana</t>
   </si>
   <si>
-    <t>Sतीश Rana</t>
+    <t>Satish Rana</t>
   </si>
   <si>
     <t>IOX1235027</t>
